--- a/data/trans_orig/IP31KM12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM12_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74607</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>112397</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>107732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>114380</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>124079</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>119206</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>97747</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>92765</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>99333</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>123628</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>118551</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>125712</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>288</t>
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>247705</t>
+          <t>210144</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241877</t>
+          <t>204418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250527</t>
+          <t>212973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7219</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1570</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6443</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6568</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7872</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56958</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55535</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51622</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47830</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54076</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62439</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115837</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111319</t>
+          <t>103250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118152</t>
+          <t>109758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7722</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68819</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64425</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>68136</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63510</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>68892</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>63866</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70462</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>74365</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>69990</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>75367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>153</t>
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142501</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137108</t>
+          <t>133076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144555</t>
+          <t>139901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5391</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6172</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6596</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38993</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36593</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>31613</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28405</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33192</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>71754</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68350</t>
+          <t>67888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73859</t>
+          <t>73796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2587</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>41738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>38470</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43615</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>88868</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91900</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97407</t>
+          <t>90774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>140248</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>138965</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>99,77%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>118157</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>111802</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>121391</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>116032</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153003</t>
+          <t>109716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>119169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>272811</t>
+          <t>256281</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267240</t>
+          <t>250522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275961</t>
+          <t>259684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5539</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11894</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>155679</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>151170</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>127941</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>124796</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>137256</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>134592</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>137900</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>152613</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>148528</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>154159</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>383</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>280552</t>
+          <t>292935</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276026</t>
+          <t>288712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282312</t>
+          <t>294610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5631</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>680565</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>674888</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>684044</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>888</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>634685</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>626735</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>641562</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>731772</t>
+          <t>591684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>741486</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1362794</t>
+          <t>1269948</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1380432</t>
+          <t>1287702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>11572</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>26399</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35083</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
